--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260819.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260819.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.44%</t>
+          <t>26.46%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.27%</t>
+          <t>8.22%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.47%</t>
+          <t>7.60%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.76%</t>
+          <t>6.39%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.52%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>4.02%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>189,186,882</t>
+          <t>5,435</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,435</t>
+          <t>184,007,458</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -792,51 +792,51 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>42,915</t>
+          <t>5,691,840</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>17,353</t>
+          <t>42,915</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -858,117 +858,117 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>73,045</t>
+          <t>17,353</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>29,970</t>
+          <t>73,045</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>19,345</t>
+          <t>29,970</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>48,645</t>
+          <t>19,345</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>11,151</t>
+          <t>48,645</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1056,68 +1056,68 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,590</t>
+          <t>11,151</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,136</t>
+          <t>20,298</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>20,298</t>
+          <t>7,590</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,154 +1129,154 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>120,885</t>
+          <t>9,136</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>17,525</t>
+          <t>120,885</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,637</t>
+          <t>17,525</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,071</t>
+          <t>18,637</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>41,210</t>
+          <t>15,071</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>35,730</t>
+          <t>41,210</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,359,494</t>
+          <t>35,730</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1315,32 +1315,10 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>175,637,500</t>
+          <t>159,710,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>4,832,346</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
